--- a/cash_register/daily_info.xlsx
+++ b/cash_register/daily_info.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reports" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,172 +462,1126 @@
           <t>Additional Info</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>1C_Quantity_Sold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>1C_Total_Sales</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31T10:00:00</t>
+          <t>2026-03-01T18:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test Cashier</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>315693</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>221907</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>173689</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Test: 10.0</t>
-        </is>
-      </c>
+        <v>15848</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Test description</t>
-        </is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>58</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1112759</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31T10:47:07</t>
+          <t>2026-03-02T18:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jrneurngunengg ergegr</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>369197</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>494313</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>180151</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>A: 45.0 | zb: 43.0</t>
-        </is>
-      </c>
+        <v>34449</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BILAD</t>
-        </is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1002664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31T10:54:47</t>
+          <t>2026-03-03T18:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jrneurngunengg ergegr</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>149080</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>179728</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>193085</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>A:3.0|B:5.0|C:7.0</t>
-        </is>
-      </c>
+        <v>9540</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ASAS</t>
-        </is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>141</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1340609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31T13:04:29</t>
+          <t>2026-03-04T18:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cashier1</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>440083</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>104028</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>143367</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>17388</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>dfe</t>
-        </is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>183</v>
+      </c>
+      <c r="K5" t="n">
+        <v>849564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31T16:30:45</t>
+          <t>2026-03-05T18:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cashier1</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>196406</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>226631</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>84127</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3:2.0</t>
-        </is>
-      </c>
+        <v>12972</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>frfrfrfrf</t>
+          <t>Mock Record</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>929864</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-06T18:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>265385</v>
+      </c>
+      <c r="D7" t="n">
+        <v>171471</v>
+      </c>
+      <c r="E7" t="n">
+        <v>76932</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11974</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1298119</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-07T18:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>191885</v>
+      </c>
+      <c r="D8" t="n">
+        <v>470037</v>
+      </c>
+      <c r="E8" t="n">
+        <v>87087</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19051</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>93</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1175421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-08T18:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>302451</v>
+      </c>
+      <c r="D9" t="n">
+        <v>476421</v>
+      </c>
+      <c r="E9" t="n">
+        <v>193410</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7461</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>194</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1494592</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-09T18:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>389404</v>
+      </c>
+      <c r="D10" t="n">
+        <v>185759</v>
+      </c>
+      <c r="E10" t="n">
+        <v>155258</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21304</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>158</v>
+      </c>
+      <c r="K10" t="n">
+        <v>557197</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-10T18:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>114994</v>
+      </c>
+      <c r="D11" t="n">
+        <v>372909</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53608</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16844</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>188</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1482611</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-11T18:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>195743</v>
+      </c>
+      <c r="D12" t="n">
+        <v>157407</v>
+      </c>
+      <c r="E12" t="n">
+        <v>58168</v>
+      </c>
+      <c r="F12" t="n">
+        <v>34247</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1222842</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-12T18:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>150982</v>
+      </c>
+      <c r="D13" t="n">
+        <v>119271</v>
+      </c>
+      <c r="E13" t="n">
+        <v>84120</v>
+      </c>
+      <c r="F13" t="n">
+        <v>31570</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>147</v>
+      </c>
+      <c r="K13" t="n">
+        <v>828305</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-13T18:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>194843</v>
+      </c>
+      <c r="D14" t="n">
+        <v>192328</v>
+      </c>
+      <c r="E14" t="n">
+        <v>186519</v>
+      </c>
+      <c r="F14" t="n">
+        <v>27152</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>189</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1035331</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>458278</v>
+      </c>
+      <c r="D15" t="n">
+        <v>287829</v>
+      </c>
+      <c r="E15" t="n">
+        <v>183466</v>
+      </c>
+      <c r="F15" t="n">
+        <v>17925</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>118</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1261499</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-15T18:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>240266</v>
+      </c>
+      <c r="D16" t="n">
+        <v>456573</v>
+      </c>
+      <c r="E16" t="n">
+        <v>162586</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44571</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>66</v>
+      </c>
+      <c r="K16" t="n">
+        <v>661542</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-16T18:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>236361</v>
+      </c>
+      <c r="D17" t="n">
+        <v>215051</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80859</v>
+      </c>
+      <c r="F17" t="n">
+        <v>28236</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>63</v>
+      </c>
+      <c r="K17" t="n">
+        <v>634334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-17T18:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>409116</v>
+      </c>
+      <c r="D18" t="n">
+        <v>343479</v>
+      </c>
+      <c r="E18" t="n">
+        <v>84196</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6180</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>80</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1476297</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-18T18:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>347942</v>
+      </c>
+      <c r="D19" t="n">
+        <v>299034</v>
+      </c>
+      <c r="E19" t="n">
+        <v>161198</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47537</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>93</v>
+      </c>
+      <c r="K19" t="n">
+        <v>579517</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19T18:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>420311</v>
+      </c>
+      <c r="D20" t="n">
+        <v>475785</v>
+      </c>
+      <c r="E20" t="n">
+        <v>164144</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34999</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>133</v>
+      </c>
+      <c r="K20" t="n">
+        <v>511607</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-20T18:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>210327</v>
+      </c>
+      <c r="D21" t="n">
+        <v>474872</v>
+      </c>
+      <c r="E21" t="n">
+        <v>132189</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20079</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>179</v>
+      </c>
+      <c r="K21" t="n">
+        <v>794320</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-21T18:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>252999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>113924</v>
+      </c>
+      <c r="E22" t="n">
+        <v>83676</v>
+      </c>
+      <c r="F22" t="n">
+        <v>35997</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>150</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1496580</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>119040</v>
+      </c>
+      <c r="D23" t="n">
+        <v>494537</v>
+      </c>
+      <c r="E23" t="n">
+        <v>172057</v>
+      </c>
+      <c r="F23" t="n">
+        <v>18673</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>120</v>
+      </c>
+      <c r="K23" t="n">
+        <v>800891</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-23T18:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>223523</v>
+      </c>
+      <c r="D24" t="n">
+        <v>373654</v>
+      </c>
+      <c r="E24" t="n">
+        <v>156005</v>
+      </c>
+      <c r="F24" t="n">
+        <v>27245</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>63</v>
+      </c>
+      <c r="K24" t="n">
+        <v>797083</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-24T18:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>232791</v>
+      </c>
+      <c r="D25" t="n">
+        <v>464733</v>
+      </c>
+      <c r="E25" t="n">
+        <v>198953</v>
+      </c>
+      <c r="F25" t="n">
+        <v>33441</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>170</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1193761</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-25T18:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>411607</v>
+      </c>
+      <c r="D26" t="n">
+        <v>230336</v>
+      </c>
+      <c r="E26" t="n">
+        <v>167376</v>
+      </c>
+      <c r="F26" t="n">
+        <v>36330</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>156</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1144020</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-26T18:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>364410</v>
+      </c>
+      <c r="D27" t="n">
+        <v>429427</v>
+      </c>
+      <c r="E27" t="n">
+        <v>106035</v>
+      </c>
+      <c r="F27" t="n">
+        <v>21056</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>98</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1159409</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-27T18:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>347230</v>
+      </c>
+      <c r="D28" t="n">
+        <v>298019</v>
+      </c>
+      <c r="E28" t="n">
+        <v>193213</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23556</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>143</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1426729</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-28T18:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>111037</v>
+      </c>
+      <c r="D29" t="n">
+        <v>452660</v>
+      </c>
+      <c r="E29" t="n">
+        <v>76865</v>
+      </c>
+      <c r="F29" t="n">
+        <v>30202</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>127</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1297280</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29T18:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>467279</v>
+      </c>
+      <c r="D30" t="n">
+        <v>326236</v>
+      </c>
+      <c r="E30" t="n">
+        <v>130450</v>
+      </c>
+      <c r="F30" t="n">
+        <v>49351</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>60</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1105357</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-30T18:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>197257</v>
+      </c>
+      <c r="D31" t="n">
+        <v>485925</v>
+      </c>
+      <c r="E31" t="n">
+        <v>57580</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33579</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Mock Record</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>85</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1111373</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
